--- a/plantillas/32.xlsx
+++ b/plantillas/32.xlsx
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/32.xlsx
+++ b/plantillas/32.xlsx
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/32.xlsx
+++ b/plantillas/32.xlsx
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>23.10.2026</t>
         </is>
       </c>
     </row>
